--- a/Unity/Assets/Config/Excel/ZuoQiShowConfig.xlsx
+++ b/Unity/Assets/Config/Excel/ZuoQiShowConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitMengJing\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF62C30-5B2E-48EC-8943-34D5E0158560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53DAC2B7-2937-4EF3-876E-D7547613A001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ZuoQiShowProto" sheetId="1" r:id="rId1"/>
@@ -194,15 +194,15 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>灵霄天马</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>青林猛虎于葱郁林间踱步，周身皮毛泛着幽光，肌肉隆起，威风凛凛，尽显百兽之王本色。</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>灵霄天马自九霄云层中疾驰而下，周身霞光萦绕，洁白羽翼舒展，鬃毛飞扬，气势撼天动地。</t>
+    <t>灵霄绝尘</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>灵霄绝尘自九霄云层中疾驰而下，周身霞光萦绕，鬃毛飞扬，气势撼天动地。</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -833,7 +833,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>29</v>
@@ -856,7 +856,7 @@
         <v>10004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E9" s="1">
         <v>5</v>
